--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/IDAHO_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/IDAHO_2020.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C49">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C97">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C138">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C142">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C148">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C199">
@@ -5971,7 +5971,7 @@
         <v>26</v>
       </c>
       <c r="D312">
-        <v>0.009954058192955589</v>
+        <v>0.009954058192955587</v>
       </c>
     </row>
     <row r="313">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C412">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C472">
